--- a/buildplan_generator/output/25-077 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-077 GENERATED BUILD PLAN.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -88,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-058, 23-059, 25-087, 23-060, 24-052</t>
+          <t>23-055, 25-083, 25-055, 23-029, 25-042</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>3</v>
+      <c r="F9" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.00 (0.67-2.20)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>6</v>
+      <c r="F10" s="9" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>5.0-9.0</t>
+          <t>ratio=0.78 (0.42-2.31)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -796,7 +794,7 @@
       <c r="E11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -806,7 +804,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>0.5-2.0</t>
+          <t>ratio=1.00 (0.40-1.50)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -833,17 +831,17 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="9" t="n">
-        <v>11</v>
+      <c r="F12" s="10" t="n">
+        <v>1.5</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>global:3.0-31.8</t>
+          <t>ratio=0.75 (n=1)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -887,8 +885,8 @@
       <c r="E14" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>7</v>
+      <c r="F14" s="9" t="n">
+        <v>6.2</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -897,7 +895,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>2.0-8.5</t>
+          <t>ratio=1.04 (0.60-2.44)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -924,17 +922,17 @@
       <c r="E15" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>7</v>
+      <c r="F15" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>4.0-10.0</t>
+          <t>ratio=0.92 (0.50-1.55)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -978,8 +976,8 @@
       <c r="E17" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>3</v>
+      <c r="F17" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -988,7 +986,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>2.0-5.5</t>
+          <t>ratio=1.00 (0.58-1.38)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1032,8 +1030,8 @@
       <c r="E19" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>1</v>
+      <c r="F19" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1042,7 +1040,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1069,17 +1067,17 @@
       <c r="E20" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="9" t="n">
-        <v>8</v>
+      <c r="F20" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-32.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1121,17 +1119,15 @@
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1158,8 +1154,8 @@
       <c r="E23" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>2</v>
+      <c r="F23" s="9" t="n">
+        <v>2.3</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1168,7 +1164,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.14 (0.88-5.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1195,8 +1191,8 @@
       <c r="E24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>1</v>
+      <c r="F24" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1205,7 +1201,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=0.92 (0.64-1.83)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1232,8 +1228,8 @@
       <c r="E25" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>3</v>
+      <c r="F25" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1242,7 +1238,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.31 (0.25-1.05)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1270,16 +1266,16 @@
         <v>4</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.69 (n=2)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1306,8 +1302,8 @@
       <c r="E27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>6.5</v>
+      <c r="F27" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1316,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>global:3.0-10.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1343,8 +1339,8 @@
       <c r="E28" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="9" t="n">
-        <v>14.5</v>
+      <c r="F28" s="11" t="n">
+        <v>3</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1353,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>global:3.0-26.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1397,17 +1393,17 @@
       <c r="E30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="11" t="n">
-        <v>2</v>
+      <c r="F30" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.75)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1434,17 +1430,17 @@
       <c r="E31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1471,17 +1467,17 @@
       <c r="E32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>2</v>
+      <c r="F32" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1509,16 +1505,16 @@
         <v>3</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>global:3.0-66.0</t>
+          <t>ratio=0.83 (0.78-1.50)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1546,16 +1542,16 @@
         <v>5</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>21.5</v>
+        <v>4.5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-61.5</t>
+          <t>ratio=0.91 (0.58-2.57)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1582,17 +1578,17 @@
       <c r="E35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="9" t="n">
-        <v>4</v>
+      <c r="F35" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-12.2</t>
+          <t>ratio=0.55 (n=2)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1637,12 +1633,12 @@
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1669,8 +1665,8 @@
       <c r="E38" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>3</v>
+      <c r="F38" s="9" t="n">
+        <v>3.2</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=0.81 (0.57-0.92)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1707,16 +1703,16 @@
         <v>5</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1743,17 +1739,17 @@
       <c r="E40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="9" t="n">
-        <v>6</v>
+      <c r="F40" s="10" t="n">
+        <v>4.8</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>global:2.5-31.5</t>
+          <t>ratio=1.58 (n=1)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1778,17 +1774,15 @@
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
-      <c r="F41" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1815,8 +1809,8 @@
       <c r="E42" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="10" t="n">
-        <v>6</v>
+      <c r="F42" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1825,7 +1819,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>1.0-11.0</t>
+          <t>ratio=1.25 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1852,17 +1846,17 @@
       <c r="E43" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>4</v>
+      <c r="F43" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>2.0-6.0</t>
+          <t>ratio=0.44 (0.42-0.50)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1889,8 +1883,8 @@
       <c r="E44" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>1</v>
+      <c r="F44" s="9" t="n">
+        <v>2.8</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1899,7 +1893,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=2.75 (2.38-3.00)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1943,17 +1937,17 @@
       <c r="E46" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>53.8</v>
+      <c r="F46" s="10" t="n">
+        <v>2.6</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>global:2.0-185.0</t>
+          <t>ratio=0.65 (n=2)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1980,17 +1974,17 @@
       <c r="E47" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="9" t="n">
-        <v>13.5</v>
+      <c r="F47" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-149.8</t>
+          <t>ratio=2.15 (n=2)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2017,17 +2011,17 @@
       <c r="E48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="9" t="n">
-        <v>5.5</v>
+      <c r="F48" s="10" t="n">
+        <v>1.5</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-14.0</t>
+          <t>ratio=0.75 (n=2)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2054,17 +2048,17 @@
       <c r="E49" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="9" t="n">
-        <v>2.8</v>
+      <c r="F49" s="10" t="n">
+        <v>1.2</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-6.5</t>
+          <t>ratio=0.59 (n=2)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2091,8 +2085,8 @@
       <c r="E50" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F50" s="11" t="n">
-        <v>2.5</v>
+      <c r="F50" s="10" t="n">
+        <v>7.3</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2101,7 +2095,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=1.47 (n=2)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2128,8 +2122,8 @@
       <c r="E51" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>5.5</v>
+      <c r="F51" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2138,7 +2132,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>2.5-7.0</t>
+          <t>ratio=0.93 (0.62-1.44)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2165,8 +2159,8 @@
       <c r="E52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="10" t="n">
-        <v>3.5</v>
+      <c r="F52" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2175,7 +2169,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>1.0-9.0</t>
+          <t>ratio=1.50 (1.33-1.50)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2202,8 +2196,8 @@
       <c r="E53" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F53" s="10" t="n">
-        <v>6.5</v>
+      <c r="F53" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2212,7 +2206,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>3.0-9.5</t>
+          <t>ratio=1.00 (0.20-1.00)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2244,12 +2238,12 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2293,17 +2287,17 @@
       <c r="E56" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="9" t="n">
-        <v>1.5</v>
+      <c r="F56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2328,17 +2322,15 @@
         </is>
       </c>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2366,12 +2358,12 @@
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2415,8 +2407,8 @@
       <c r="E60" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="10" t="n">
-        <v>4.5</v>
+      <c r="F60" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2425,7 +2417,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.50 (1.00-2.25)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2452,8 +2444,8 @@
       <c r="E61" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F61" s="10" t="n">
-        <v>12</v>
+      <c r="F61" s="9" t="n">
+        <v>6.3</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2462,7 +2454,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>4.0-21.0</t>
+          <t>ratio=1.05 (0.77-1.71)</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2490,12 +2482,12 @@
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2523,12 +2515,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2555,8 +2547,8 @@
       <c r="E64" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F64" s="10" t="n">
-        <v>7.8</v>
+      <c r="F64" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2565,7 +2557,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>5.0-10.0</t>
+          <t>ratio=0.80 (0.25-1.00)</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2593,12 +2585,12 @@
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2642,8 +2634,8 @@
       <c r="E67" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="10" t="n">
-        <v>2.5</v>
+      <c r="F67" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2652,7 +2644,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.5</t>
+          <t>ratio=3.00 (2.00-4.00)</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2680,12 +2672,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2712,8 +2704,8 @@
       <c r="E69" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="10" t="n">
-        <v>4</v>
+      <c r="F69" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -2722,7 +2714,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.5</t>
+          <t>ratio=1.25 (0.83-1.50)</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2736,7 +2728,7 @@
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>276.9</v>
+        <v>140.6</v>
       </c>
     </row>
   </sheetData>
@@ -2804,7 +2796,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-058, 23-059, 25-087, 23-060, 24-052</t>
+          <t>23-055, 25-083, 25-055, 23-029, 25-042</t>
         </is>
       </c>
     </row>
@@ -4505,35 +4497,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-058</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-059</t>
+          <t>25-083</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-087</t>
+          <t>25-055</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>23-029</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-052</t>
+          <t>25-042</t>
         </is>
       </c>
     </row>
@@ -4588,23 +4580,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4622,19 +4610,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 24-052, 25-087</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4648,7 +4632,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4657,12 +4641,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.00 (0.67-2.20)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4662,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4687,12 +4671,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.0-9.0</t>
+          <t>ratio=0.78 (0.42-2.31)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4701,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.5-2.0</t>
+          <t>ratio=1.00 (0.40-1.50)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -4738,21 +4722,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>global:3.0-31.8</t>
+          <t>ratio=0.75 (n=1)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4752,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4777,12 +4761,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.0-8.5</t>
+          <t>ratio=1.04 (0.60-2.44)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -4798,21 +4782,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.0-10.0</t>
+          <t>ratio=0.92 (0.50-1.55)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-087, 24-052</t>
+          <t>25-083, 25-055, 25-042</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4812,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4837,12 +4821,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.0-5.5</t>
+          <t>ratio=1.00 (0.58-1.38)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4842,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4867,12 +4851,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -4888,21 +4872,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>global:0.5-32.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
@@ -4918,23 +4902,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4948,7 +4928,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4957,12 +4937,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.14 (0.88-5.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-087, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4958,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4987,12 +4967,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=0.92 (0.64-1.83)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5008,7 +4988,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5017,12 +4997,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.31 (0.25-1.05)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5038,21 +5018,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.69 (n=2)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>24-052, 23-059, 23-058</t>
+          <t>25-083, 23-055</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5048,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5077,12 +5057,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>global:3.0-10.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5078,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>14.5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5107,12 +5087,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>global:3.0-26.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5128,23 +5108,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5158,21 +5134,21 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.75)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-087, 23-060</t>
+          <t>25-083, 25-042, 23-029</t>
         </is>
       </c>
     </row>
@@ -5192,17 +5168,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-087, 23-060</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5218,21 +5194,21 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.75-1.00)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-087, 23-060</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5248,21 +5224,21 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>global:3.0-66.0</t>
+          <t>ratio=0.83 (0.78-1.50)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5278,21 +5254,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.5</v>
+        <v>4.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>global:1.0-61.5</t>
+          <t>ratio=0.91 (0.58-2.57)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5308,21 +5284,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>global:0.5-12.2</t>
+          <t>ratio=0.55 (n=2)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083, 23-029</t>
         </is>
       </c>
     </row>
@@ -5342,19 +5318,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>23-060, 25-087</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5368,7 +5340,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5377,12 +5349,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=0.81 (0.57-0.92)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5398,21 +5370,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24-052, 23-060, 23-059, 23-058</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
@@ -5428,21 +5400,21 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>global:2.5-31.5</t>
+          <t>ratio=1.58 (n=1)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
@@ -5458,23 +5430,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5488,7 +5456,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5497,12 +5465,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.0-11.0</t>
+          <t>ratio=1.25 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5518,21 +5486,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0-6.0</t>
+          <t>ratio=0.44 (0.42-0.50)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-087, 23-060</t>
+          <t>25-083, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5516,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,12 +5525,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=2.75 (2.38-3.00)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5578,21 +5546,21 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>53.8</v>
+        <v>2.6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>global:2.0-185.0</t>
+          <t>ratio=0.65 (n=2)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083, 23-055</t>
         </is>
       </c>
     </row>
@@ -5608,21 +5576,21 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>global:1.0-149.8</t>
+          <t>ratio=2.15 (n=2)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083, 23-055</t>
         </is>
       </c>
     </row>
@@ -5638,21 +5606,21 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>global:0.5-14.0</t>
+          <t>ratio=0.75 (n=2)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083, 23-055</t>
         </is>
       </c>
     </row>
@@ -5668,21 +5636,21 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>global:1.0-6.5</t>
+          <t>ratio=0.59 (n=2)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-083, 23-055</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5666,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.5</v>
+        <v>7.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5707,12 +5675,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.5-2.5</t>
+          <t>ratio=1.47 (n=2)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-087</t>
+          <t>25-083, 23-029</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5696,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5737,12 +5705,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2.5-7.0</t>
+          <t>ratio=0.93 (0.62-1.44)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5726,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5767,12 +5735,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0-9.0</t>
+          <t>ratio=1.50 (1.33-1.50)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-029</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5756,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,12 +5765,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.0-9.5</t>
+          <t>ratio=1.00 (0.20-1.00)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-029</t>
         </is>
       </c>
     </row>
@@ -5822,17 +5790,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-042, 23-055</t>
         </is>
       </c>
     </row>
@@ -5848,21 +5816,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>23-029</t>
         </is>
       </c>
     </row>
@@ -5878,23 +5846,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5912,19 +5876,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>23-060, 25-087</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5938,7 +5898,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5947,12 +5907,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.50 (1.00-2.25)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5928,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>6.3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5977,12 +5937,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.0-21.0</t>
+          <t>ratio=1.05 (0.77-1.71)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -6002,19 +5962,15 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 24-052, 25-087</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6032,19 +5988,15 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>23-060, 25-087</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6058,7 +6010,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6067,12 +6019,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>5.0-10.0</t>
+          <t>ratio=0.80 (0.25-1.00)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-087, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-029</t>
         </is>
       </c>
     </row>
@@ -6092,19 +6044,15 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 25-087</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6118,7 +6066,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6127,12 +6075,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2.0-3.5</t>
+          <t>ratio=3.00 (2.00-4.00)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 25-042, 23-055, 23-029</t>
         </is>
       </c>
     </row>
@@ -6152,19 +6100,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 24-052, 25-087</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6178,7 +6122,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6187,12 +6131,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2.0-4.5</t>
+          <t>ratio=1.25 (0.83-1.50)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-087, 24-052, 23-060, 23-059, 23-058</t>
+          <t>25-083, 23-055, 23-029</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-077 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-077 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +76,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-055, 25-083, 25-055, 23-029, 25-042</t>
+          <t>25-055, 23-055, 25-083, 23-097, 23-094</t>
         </is>
       </c>
     </row>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-2.20)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +751,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.42-2.31)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -795,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -804,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.40-1.50)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -831,17 +824,17 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>1.5</v>
+      <c r="F12" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=1)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -886,7 +879,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -895,7 +888,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.60-2.44)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -923,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -932,7 +925,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.50-1.55)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -977,7 +970,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -986,7 +979,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.58-1.38)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1031,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1040,7 +1033,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1067,17 +1060,17 @@
       <c r="E20" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>3</v>
+      <c r="F20" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1122,12 +1115,12 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1164,7 +1157,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.14 (0.88-5.00)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1192,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1201,7 +1194,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.64-1.83)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1229,7 +1222,7 @@
         <v>5</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1238,7 +1231,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.31 (0.25-1.05)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1265,17 +1258,17 @@
       <c r="E26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>2.8</v>
+      <c r="F26" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.69 (n=2)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1302,17 +1295,15 @@
       <c r="E27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1339,17 +1330,17 @@
       <c r="E28" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>3</v>
+      <c r="F28" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1394,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1403,7 +1394,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.75)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1431,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1431,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1468,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1477,7 +1468,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1505,7 +1496,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1505,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.78-1.50)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1542,7 +1533,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1551,7 +1542,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.91 (0.58-2.57)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1578,17 +1569,17 @@
       <c r="E35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>1.6</v>
+      <c r="F35" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.55 (n=2)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1633,12 +1624,12 @@
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1666,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1675,7 +1666,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.57-0.92)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1702,17 +1693,17 @@
       <c r="E39" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>5</v>
+      <c r="F39" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1739,17 +1730,17 @@
       <c r="E40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>4.8</v>
+      <c r="F40" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.58 (n=1)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1777,12 +1768,12 @@
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1819,7 +1810,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.50)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1847,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1856,7 +1847,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.44 (0.42-0.50)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1883,17 +1874,17 @@
       <c r="E44" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="9" t="n">
-        <v>2.8</v>
+      <c r="F44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.75 (2.38-3.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1937,17 +1928,17 @@
       <c r="E46" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>2.6</v>
+      <c r="F46" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.65 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1974,17 +1965,17 @@
       <c r="E47" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>10.8</v>
+      <c r="F47" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.15 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2011,17 +2002,17 @@
       <c r="E48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>1.5</v>
+      <c r="F48" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2048,17 +2039,15 @@
       <c r="E49" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.59 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2085,17 +2074,17 @@
       <c r="E50" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>7.3</v>
+      <c r="F50" s="9" t="n">
+        <v>3.4</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.47 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2123,7 +2112,7 @@
         <v>5</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2132,7 +2121,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.93 (0.62-1.44)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2160,7 +2149,7 @@
         <v>3</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2169,7 +2158,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.33-1.50)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2197,7 +2186,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2206,7 +2195,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.20-1.00)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2233,17 +2222,17 @@
       <c r="E54" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>1</v>
+      <c r="F54" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2287,17 +2276,17 @@
       <c r="E56" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="10" t="n">
-        <v>1</v>
+      <c r="F56" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2325,12 +2314,12 @@
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2358,12 +2347,12 @@
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2408,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2417,7 +2406,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-2.25)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2445,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2454,7 +2443,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.05 (0.77-1.71)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2482,12 +2471,12 @@
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2515,12 +2504,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2548,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>4</v>
+        <v>13.1</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2557,7 +2546,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.25-1.00)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2585,12 +2574,12 @@
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2635,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2644,7 +2633,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-4.00)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2672,12 +2661,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2705,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -2714,7 +2703,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.83-1.50)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2728,7 +2717,7 @@
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>140.6</v>
+        <v>105.3</v>
       </c>
     </row>
   </sheetData>
@@ -2796,7 +2785,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-055, 25-083, 25-055, 23-029, 25-042</t>
+          <t>25-055, 23-055, 25-083, 23-097, 23-094</t>
         </is>
       </c>
     </row>
@@ -4497,35 +4486,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-055</t>
+          <t>25-055</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-083</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-055</t>
+          <t>25-083</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-029</t>
+          <t>23-097</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-042</t>
+          <t>23-094</t>
         </is>
       </c>
     </row>
@@ -4584,15 +4573,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4610,15 +4603,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4632,7 +4629,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4641,12 +4638,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-2.20)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4659,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4671,12 +4668,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.42-2.31)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4689,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4701,12 +4698,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.40-1.50)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 23-055, 23-029</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4722,21 +4719,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=1)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-083</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4749,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4761,12 +4758,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.60-2.44)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4791,12 +4788,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.50-1.55)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4809,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4821,12 +4818,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.58-1.38)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4839,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4851,12 +4848,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -4872,21 +4869,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23-055</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -4906,15 +4903,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4937,12 +4938,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.14 (0.88-5.00)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4959,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4967,12 +4968,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.64-1.83)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4989,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4997,12 +4998,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=0.31 (0.25-1.05)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-083, 25-055, 25-042, 23-055, 23-029</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5018,21 +5019,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=0.69 (n=2)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-083, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5048,21 +5049,21 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5078,21 +5079,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5112,15 +5113,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5134,7 +5139,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5143,12 +5148,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.75)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-029</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5169,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5173,12 +5178,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5199,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5203,12 +5208,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.00)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5229,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5233,12 +5238,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.78-1.50)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-083, 23-055, 23-029</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5259,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5263,12 +5268,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=0.91 (0.58-2.57)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-083, 23-055, 23-029</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5284,21 +5289,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=0.55 (n=2)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-083, 23-029</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5318,15 +5323,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5340,7 +5349,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5349,12 +5358,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.57-0.92)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5370,21 +5379,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5400,21 +5409,21 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.58 (n=1)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5434,15 +5443,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5465,12 +5478,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-2.50)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5499,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5495,12 +5508,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=0.44 (0.42-0.50)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-083, 23-055, 23-029</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5516,21 +5529,21 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=2.75 (2.38-3.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5546,21 +5559,21 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=0.65 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-083, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5576,21 +5589,21 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=2.15 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-083, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5606,21 +5619,21 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-083, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5636,21 +5649,21 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.59 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-083, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5666,21 +5679,21 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=1.47 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-083, 23-029</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5709,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5705,12 +5718,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=0.93 (0.62-1.44)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5739,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5735,12 +5748,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.33-1.50)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-029</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5769,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5765,12 +5778,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.20-1.00)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-029</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5786,21 +5799,21 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-042, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5816,21 +5829,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>23-029</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5850,15 +5863,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5876,15 +5893,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5898,7 +5919,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5907,12 +5928,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-2.25)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-042, 23-055, 23-029</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5949,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5937,12 +5958,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=1.05 (0.77-1.71)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5962,15 +5983,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5988,15 +6013,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6010,7 +6039,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>13.1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6019,12 +6048,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.25-1.00)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-029</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6044,15 +6073,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6066,7 +6099,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6075,12 +6108,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-4.00)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-083, 25-042, 23-055, 23-029</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6100,15 +6133,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6122,7 +6159,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6131,12 +6168,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.83-1.50)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-083, 23-055, 23-029</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-077 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-077 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -788,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -825,7 +825,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -879,7 +879,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -916,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -970,7 +970,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1024,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1185,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1222,7 +1222,7 @@
         <v>5</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1259,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1459,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1496,7 +1496,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1533,7 +1533,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1570,7 +1570,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1657,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1731,7 +1731,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1801,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1838,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1929,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2112,7 +2112,7 @@
         <v>5</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2149,7 +2149,7 @@
         <v>3</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2186,7 +2186,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2434,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2537,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>105.3</v>
+        <v>112.5</v>
       </c>
     </row>
   </sheetData>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
